--- a/data/Reviewer_papers.xlsx
+++ b/data/Reviewer_papers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/0_Reviewer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/javier/Library/CloudStorage/OneDrive-UniversidadPolitécnicadeMadrid/Universidad/Publicaciones/0_Reviewer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_4033099B514F7C8FEF6FE0F54B10B67B29611144" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7569EDF5-20F2-164B-ADDE-88ED9BE2D338}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4C9CC7-0D0B-B147-B87D-8FEC67FA8DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="2540" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="900" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="37">
   <si>
     <t>Tipo</t>
   </si>
@@ -131,15 +131,25 @@
   </si>
   <si>
     <t>IEEE Transactions on Network and Service Management</t>
+  </si>
+  <si>
+    <t>Behavior Research Methods</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -216,41 +226,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -565,7 +579,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" style="11" customWidth="1"/>
@@ -1049,6 +1063,20 @@
         <v>9</v>
       </c>
     </row>
+    <row r="28" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
